--- a/tests/Fixtures/Inventory/SYNTHETIC_inventory_with_errors.xlsx
+++ b/tests/Fixtures/Inventory/SYNTHETIC_inventory_with_errors.xlsx
@@ -24,7 +24,7 @@
     <definedName name="OperatingModels">Lists!$A$2:$A$3</definedName>
     <definedName name="PropertyStatuses">Lists!$B$2:$B$6</definedName>
     <definedName name="SpaceTypes">Lists!$C$2:$C$7</definedName>
-    <definedName name="InventoryModes">Lists!$D$2:$D$4</definedName>
+    <definedName name="InventoryModes">Lists!$D$2:$D$5</definedName>
     <definedName name="SpaceStatuses">Lists!$E$2:$E$5</definedName>
     <definedName name="YesNo">Lists!$F$2:$F$3</definedName>
     <definedName name="Weekdays">Lists!$G$2:$G$8</definedName>
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Template SG-INV-1.1 · draft generated 2026-10-24 · status: DRAFT pending owner questions Q-OW-1 (floor allocation), Q-OW-2 (property grouping), Q-OW-7 (hybrid zones)</t>
+          <t>Template SG-INV-1.2 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1. Fill the sheets in order: Property → Buildings → Hours → Floors → Spaces → Seats (only 'Per seat' spaces) → Occupancy → Amenities.</t>
+          <t>1. Fill the sheets in order: Property → Buildings → Hours → Floors → Spaces → Seats ('Per seat' and 'Hybrid' spaces) → Occupancy → Amenities.</t>
         </is>
       </c>
     </row>
@@ -648,14 +648,14 @@
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Space type → allowed inventory modes (proposed defaults, ADR-0013): Private cabin, Meeting room, Conference / training room, Office suite → Whole space · Dedicated desk zone → Per seat · Flexible seating zone → Pooled or Per seat.</t>
+          <t>Space type → allowed inventory modes (proposed defaults, ADR-0013): Private cabin, Meeting room, Conference / training room, Office suite → Whole space · Dedicated desk zone → Per seat or Hybrid · Flexible seating zone → Pooled, Per seat or Hybrid.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Product category → required inventory mode: Private cabins / private offices, Meeting rooms, Conference and training rooms, Managed offices for enterprises → Whole space · Dedicated desks → Per seat · Hot desks / flexible seating → Pooled or Per seat · Virtual office / business address → not a physical space (never listed under sellable_as).</t>
+          <t>Product category → required inventory mode: Private cabins / private offices, Meeting rooms, Conference and training rooms, Managed offices for enterprises → Whole space · Dedicated desks → Per seat or Hybrid · Hot desks / flexible seating → Pooled, Per seat or Hybrid · Virtual office / business address → not a physical space (never listed under sellable_as).</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Seats: Individual seats, only for spaces with inventory mode 'Per seat'.</t>
+          <t>Seats: Individual seats, only for spaces with inventory mode 'Per seat' or 'Hybrid (seats + pool)'.</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1006,11 @@
           <t>Meeting room</t>
         </is>
       </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid (seats + pool)</t>
+        </is>
+      </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Decommissioned</t>
@@ -1120,7 +1125,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>SG-INV-1.1</t>
+          <t>SG-INV-1.2</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,7 +1396,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,7 +1426,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,7 +1456,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1481,7 +1486,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1541,7 +1546,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1571,7 +1576,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1631,7 +1636,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1661,7 +1666,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1691,7 +1696,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1721,16 +1726,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>seat_label</t>
+          <t>seats_allocated</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>V-145</t>
+          <t>V-150</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1740,7 +1745,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seat label given for a 'Whole space' cabin.</t>
+          <t>Hybrid zone: 2 assigned + 5 pooled + 4 pooled seats exceed 10 active seats (BR-AV-3d).</t>
         </is>
       </c>
     </row>
@@ -1751,24 +1756,54 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>seat_label</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>V-145</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Seat label given for a 'Whole space' cabin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>contract_reference</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>W-170</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>warning</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Looks like personal data (an email address) in contract_reference.</t>
         </is>
@@ -1859,7 +1894,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Required. City name as it should appear publicly (see owner question Q-OW-4).</t>
+          <t>Required. Official current city name, e.g. Noida, Gurugram, Delhi, Faridabad, Ghaziabad.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -11001,7 +11036,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -11134,7 +11169,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Required. Whole space = one occupant; Per seat = each seat tracked; Pooled = shared capacity.</t>
+          <t>Required. Whole space = one occupant; Per seat = each seat tracked; Pooled = shared capacity; Hybrid = some seats assigned, the rest shared.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -12086,12 +12121,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA</t>
+          <t>SYN-ALPHA</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-A</t>
+          <t>SYN-ALPHA-B</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -12099,29 +12134,29 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-01-PC-01</t>
+          <t>SYN-ALPHA-B1-HY-01</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Cabin 1.01</t>
+          <t>Hybrid desks B1</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Private cabin</t>
+          <t>Flexible seating zone</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Whole space</t>
+          <t>Hybrid (seats + pool)</t>
         </is>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>420</v>
+        <v>700</v>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
@@ -12130,12 +12165,12 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Private cabins / private offices</t>
+          <t>Dedicated desks; Hot desks / flexible seating</t>
         </is>
       </c>
       <c r="M16" s="12" t="n"/>
@@ -12164,17 +12199,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>SYN-BETA-01-MR-01</t>
+          <t>SYN-BETA-01-PC-01</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Meeting room Pine</t>
+          <t>Cabin 1.01</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Meeting room</t>
+          <t>Private cabin</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -12186,7 +12221,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
@@ -12200,23 +12235,13 @@
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>Meeting rooms</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>Video conferencing screen; Whiteboard</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="P17" s="12" t="n">
-        <v>480</v>
-      </c>
+          <t>Private cabins / private offices</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
       <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>SYNTHETIC test data</t>
@@ -12226,30 +12251,30 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA</t>
+          <t>SYN-BETA</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-A</t>
+          <t>SYN-BETA-A</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-01</t>
+          <t>SYN-BETA-01-MR-01</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Cabin 3.01</t>
+          <t>Meeting room Pine</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Private cabin</t>
+          <t>Meeting room</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -12258,7 +12283,7 @@
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>220</v>
@@ -12270,22 +12295,28 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>Private cabins / private offices</t>
+          <t>Meeting rooms</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Natural light</t>
-        </is>
-      </c>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
+          <t>Video conferencing screen; Whiteboard</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>480</v>
+      </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>SYNTHETIC test data</t>
@@ -12308,7 +12339,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-90</t>
+          <t>SYN-ALPHA-03-PC-01</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -12318,7 +12349,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Cabin</t>
+          <t>Private cabin</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -12377,7 +12408,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-91</t>
+          <t>SYN-ALPHA-03-PC-90</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -12387,7 +12418,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Private cabin</t>
+          <t>Cabin</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -12396,7 +12427,7 @@
         </is>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>220</v>
@@ -12442,11 +12473,11 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-07-PC-01</t>
+          <t>SYN-ALPHA-03-PC-91</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -12465,7 +12496,7 @@
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>220</v>
@@ -12511,33 +12542,33 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-07-PC-01</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Cabin 3.01</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Private cabin</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Whole space</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>SYN-ALPHA-04-MR-09</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Meeting room Cedar</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Meeting room</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Whole space</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="I22" s="12" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
@@ -12551,20 +12582,16 @@
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>Meeting rooms</t>
+          <t>Private cabins / private offices</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
-          <t>Video conferencing screen; Whiteboard</t>
-        </is>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O22" s="12" t="n">
-        <v>30</v>
-      </c>
+          <t>Natural light</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
       <c r="P22" s="12" t="n"/>
       <c r="Q22" s="12" t="inlineStr">
         <is>
@@ -12588,7 +12615,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-04-MR-10</t>
+          <t>SYN-ALPHA-04-MR-09</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -12603,7 +12630,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Per seat</t>
+          <t>Whole space</t>
         </is>
       </c>
       <c r="H23" s="12" t="n">
@@ -12638,9 +12665,7 @@
       <c r="O23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="P23" s="12" t="n">
-        <v>480</v>
-      </c>
+      <c r="P23" s="12" t="n"/>
       <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>SYNTHETIC test data</t>
@@ -12659,53 +12684,63 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-FS-02</t>
+          <t>SYN-ALPHA-04-MR-10</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Flexible lounge</t>
+          <t>Meeting room Cedar</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Flexible seating zone</t>
+          <t>Meeting room</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Pooled</t>
+          <t>Per seat</t>
         </is>
       </c>
       <c r="H24" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>Meeting rooms</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>Video conferencing screen; Whiteboard</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O24" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>Dedicated desks</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
+      <c r="P24" s="12" t="n">
+        <v>480</v>
+      </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>SYNTHETIC test data</t>
@@ -12728,29 +12763,29 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-92</t>
+          <t>SYN-ALPHA-03-FS-02</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Cabin 3.01</t>
+          <t>Flexible lounge</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Private cabin</t>
+          <t>Flexible seating zone</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Whole space</t>
+          <t>Pooled</t>
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>220</v>
+        <v>1800</v>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
@@ -12764,14 +12799,10 @@
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>Private cabins / private offices</t>
-        </is>
-      </c>
-      <c r="M25" s="12" t="inlineStr">
-        <is>
-          <t>Natural light; Jacuzzi</t>
-        </is>
-      </c>
+          <t>Dedicated desks</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="n"/>
       <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
       <c r="P25" s="12" t="n"/>
@@ -12782,23 +12813,73 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-A</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-03-PC-92</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Cabin 3.01</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Private cabin</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Whole space</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>Private cabins / private offices</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>Natural light; Jacuzzi</t>
+        </is>
+      </c>
       <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
       <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
+      <c r="Q26" s="12" t="inlineStr">
+        <is>
+          <t>SYNTHETIC test data</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -16240,7 +16321,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Required. Per-seat space code from the Spaces sheet.</t>
+          <t>Required. Per-seat or hybrid space code from the Spaces sheet.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -16478,69 +16559,189 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>H-05</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>H-06</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>H-07</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>H-08</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>H-09</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>H-10</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>SYN-ALPHA-04-MR-01</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>X-01</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="12" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -17506,7 +17707,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Optional. Per-seat spaces only: the seat allocated.</t>
+          <t>Optional. Per-seat or hybrid spaces: the seat assigned. Leave blank for pooled seats in a hybrid zone.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -17777,23 +17978,27 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-01</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n"/>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SYN-AGR-0090</t>
+          <t>SYN-AGR-0007</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>46174</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>46143</v>
+        <v>46538</v>
       </c>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="12" t="inlineStr">
@@ -17805,23 +18010,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-02</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n"/>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SYN-AGR-0099</t>
+          <t>SYN-AGR-0007</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>46387</v>
+        <v>46538</v>
       </c>
       <c r="G12" s="13" t="n"/>
       <c r="H12" s="12" t="inlineStr">
@@ -17833,100 +18042,172 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-03-PC-01</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SYN-AGR-0091</t>
+          <t>SYN-AGR-0008</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>46753</v>
+        <v>46204</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>46934</v>
+        <v>46568</v>
       </c>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>SYN-ALPHA-04-OS-01</t>
+          <t>SYN-ALPHA-03-PC-01</t>
         </is>
       </c>
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>jane.doe@example.com</t>
+          <t>SYN-AGR-0090</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>47484</v>
-      </c>
-      <c r="F14" s="13" t="n"/>
+        <v>46174</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>46143</v>
+      </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-03-PC-02</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0099</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>46387</v>
+      </c>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-B1-HY-01</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0098</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>46235</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>46418</v>
+      </c>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-03-PC-01</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>SYN-AGR-0091</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>46753</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>46934</v>
+      </c>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
           <t>Reserved</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="12" t="n"/>
-    </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>SYN-ALPHA-04-OS-01</t>
+        </is>
+      </c>
       <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="13" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>jane.doe@example.com</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>47484</v>
+      </c>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>

--- a/tests/Fixtures/Inventory/SYNTHETIC_inventory_with_errors.xlsx
+++ b/tests/Fixtures/Inventory/SYNTHETIC_inventory_with_errors.xlsx
@@ -557,7 +557,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Template SG-INV-1.2 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
+          <t>Template SG-INV-1.3 · draft generated 2026-10-24 · status: DRAFT; floors per property still to be supplied (Q-OW-1). Each address is its own property; current properties are owned and operated.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>SG-INV-1.2</t>
+          <t>SG-INV-1.3</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>centre_manager_email</t>
+          <t>property_manager_email</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Optional. Work email of the SmartGro centre manager (staff only).</t>
+          <t>Optional. Work email of the SmartGro Property Manager (staff only).</t>
         </is>
       </c>
     </row>
